--- a/CloudWatchLogsからJP1までのアラート通知.xlsx
+++ b/CloudWatchLogsからJP1までのアラート通知.xlsx
@@ -1758,7 +1758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2302,225 +2302,247 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31" ht="59" customHeight="1">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>評価窓の上限</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Period × EvaluationPeriods</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>期間が 3600 秒未満なら最大 1 日。期間が 3600 秒以上なら最大 7 日</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>300 秒 × 3 は 15 分なので、この上限には届かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="59" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>DatapointsToAlarm を省略すると、評価期間のすべてが違反である必要がある、という動作になる。短いスパイクで鳴りすぎるときは、N を 3、M を 2 のようにする。2回は連続していなくてよい。直近3個のうち、どれか2個が線を超えていれば鳴る。</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="25" t="n"/>
-      <c r="D31" s="25" t="n"/>
-    </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>期間300秒、N=3、M=2 なら、見る範囲はおおよそ15分で、そのうち2個の5分箱が超えていれば鳴る。検知は遅くなる代わりに、1回きりのバーストでは鳴りにくい。</t>
         </is>
       </c>
       <c r="B32" s="25" t="n"/>
       <c r="C32" s="25" t="n"/>
       <c r="D32" s="25" t="n"/>
     </row>
-    <row r="33" ht="59" customHeight="1">
+    <row r="33" ht="42" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>評価のとき、CloudWatch は指定した N 個より少し多めの点を取りにいく。直近が欠けていると、評価範囲の中の、より古い実在する点を使って判定することがある。「点がない枠は無かったこと」とだけ覚えると、実際の遷移とずれる。欠測の設定とデフォルト値で、欠け方を決めておく。</t>
+          <t>期間300秒、N=3、M=2 なら、見る範囲はおおよそ15分で、そのうち2個の5分箱が超えていれば鳴る。検知は遅くなる代わりに、1回きりのバーストでは鳴りにくい。</t>
         </is>
       </c>
       <c r="B33" s="25" t="n"/>
       <c r="C33" s="25" t="n"/>
       <c r="D33" s="25" t="n"/>
     </row>
-    <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+    <row r="34" ht="59" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>評価のとき、CloudWatch は指定した N 個より少し多めの点を取りにいく。直近が欠けていると、評価範囲の中の、より古い実在する点を使って判定することがある。「点がない枠は無かったこと」とだけ覚えると、実際の遷移とずれる。欠測の設定とデフォルト値で、欠け方を決めておく。</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="25" t="n"/>
+    </row>
+    <row r="35" ht="27" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>欠測の四つの扱い</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n"/>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="29" t="n"/>
-    </row>
-    <row r="35" ht="59" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+    </row>
+    <row r="36" ht="59" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>欠けた点をどう見るか</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>件数アラームでの意味</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>notBreaching</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>線の内側（良い）</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>静かな時間を正常とみなす。件数ではこれが基本</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="21" t="inlineStr">
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>breaching</t>
         </is>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>線の外側（悪い）</t>
         </is>
       </c>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>点が欠けると鳴る。心拍のように「届き続けるべきもの」向き</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>ignore</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>今の状態を維持する材料にしない</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>状態を急に変えたくないとき</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="59" customHeight="1">
-      <c r="A39" s="21" t="inlineStr">
+    <row r="40" ht="59" customHeight="1">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>評価範囲が全部欠けると INSUFFICIENT_DATA。既定</t>
         </is>
       </c>
-      <c r="C39" s="21" t="inlineStr">
+      <c r="C40" s="21" t="inlineStr">
         <is>
           <t>作成直後や、監視そのものが止まったときのデータ不足</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="41"/>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>notBreaching だけに頼ると、ログの送信が止まって日記が来なくなっても、エラー件数のベルは OK のままである。見張りが寝ていることに気づけない。</t>
-        </is>
-      </c>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="25" t="n"/>
-      <c r="D41" s="25" t="n"/>
-    </row>
-    <row r="42" ht="59" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>別のアラームを一本足す。名前空間 AWS/Logs の IncomingLogEvents（または IncomingBytes）を、そのロググループのディメンションで見る。入ってくる件数が 0 に落ちたら、JP1 へ「ログが届いていない」を出す。これはエラー件数とは別の出来事である。同じ SNS と SQS を使ってよい。</t>
         </is>
       </c>
       <c r="B42" s="25" t="n"/>
       <c r="C42" s="25" t="n"/>
       <c r="D42" s="25" t="n"/>
     </row>
-    <row r="43" ht="42" customHeight="1">
+    <row r="43" ht="59" customHeight="1">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>デフォルト値 0 は、「ログは来たが一致はゼロ」を埋める。IncomingLogEvents は、「ログが来たか」を見る。両方あると、静けさと、監視の停止を区別できる。</t>
+          <t>別のアラームを一本足す。名前空間 AWS/Logs の IncomingLogEvents（または IncomingBytes）を、そのロググループのディメンションで見る。入ってくる件数が 0 に落ちたら、JP1 へ「ログが届いていない」を出す。これはエラー件数とは別の出来事である。同じ SNS と SQS を使ってよい。</t>
         </is>
       </c>
       <c r="B43" s="25" t="n"/>
       <c r="C43" s="25" t="n"/>
       <c r="D43" s="25" t="n"/>
     </row>
-    <row r="44" ht="27" customHeight="1">
-      <c r="A44" s="26" t="inlineStr">
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>デフォルト値 0 は、「ログは来たが一致はゼロ」を埋める。IncomingLogEvents は、「ログが来たか」を見る。両方あると、静けさと、監視の停止を区別できる。</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+    </row>
+    <row r="45" ht="27" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>鳴ったあとに鳴り続けないこと</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n"/>
-      <c r="C44" s="29" t="n"/>
-      <c r="D44" s="29" t="n"/>
-    </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="B45" s="29" t="n"/>
+      <c r="C45" s="29" t="n"/>
+      <c r="D45" s="29" t="n"/>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>状態が ALARM のあいだは、期間が何回来ても SNS は出ない。JP1 で「まだ続いている」と何度も札を上げたい場合は、この経路だけでは足りない。設計は次のどちらかにする。</t>
         </is>
       </c>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="25" t="n"/>
-    </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>・状態が変わったときだけ JP1 へ出す。継続は JP1 側の対処状況で持つ。この経路の自然な使い方である。</t>
-        </is>
-      </c>
-      <c r="B46" s="30" t="n"/>
-      <c r="C46" s="30" t="n"/>
-      <c r="D46" s="30" t="n"/>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="25" t="n"/>
+      <c r="D46" s="25" t="n"/>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>・毎回の件数が欲しい。その場合はアラームを介さず、別の定期処理でメトリクスを読む。今回の「閾値を超えたら」という要件とは別物である。</t>
+          <t>・状態が変わったときだけ JP1 へ出す。継続は JP1 側の対処状況で持つ。この経路の自然な使い方である。</t>
         </is>
       </c>
       <c r="B47" s="30" t="n"/>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="30" t="n"/>
     </row>
-    <row r="48" ht="25" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>・毎回の件数が欲しい。その場合はアラームを介さず、別の定期処理でメトリクスを読む。今回の「閾値を超えたら」という要件とは別物である。</t>
+        </is>
+      </c>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="30" t="n"/>
+      <c r="D48" s="30" t="n"/>
+    </row>
+    <row r="49" ht="25" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>復旧で OK に戻り、再び超えると、また ALARM へ遷移するので、そのときはもう一度届く。</t>
         </is>
       </c>
-      <c r="B48" s="25" t="n"/>
-      <c r="C48" s="25" t="n"/>
-      <c r="D48" s="25" t="n"/>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25" t="n"/>
+      <c r="D49" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A35:D35"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A49:D49"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A46:D46"/>
@@ -2926,7 +2948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3141,64 +3163,74 @@
       </c>
     </row>
     <row r="15"/>
-    <row r="16" ht="59" customHeight="1">
+    <row r="16" ht="76" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>トピックのアクセスポリシーに、CloudWatch からの sns:Publish が無いと、アラームはアクションを持っていても放送できない。アラーム作成画面からトピックを作ると付くことが多い。トピックを先に手作りした場合は、自分で入れる。</t>
+          <t>SNS から SQS へ届けるとき、キュー属性の最大メッセージサイズは見ない。効くのはトピックの MaximumMessageSize である。アラームの JSON は数 KB なので、トピックは既定の 256 KiB のままでよい。1 MiB へ上げると、購読先が SQS、Lambda、Data Firehose だけになり、購読は 100 までに減る。メール購読を同じトピックへ足す予定があるなら、上げない。</t>
         </is>
       </c>
       <c r="B16" s="25" t="n"/>
       <c r="C16" s="25" t="n"/>
     </row>
-    <row r="17" ht="25" customHeight="1">
+    <row r="17" ht="59" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>条件は次の二つを両方入れる。</t>
+          <t>トピックのアクセスポリシーに、CloudWatch からの sns:Publish が無いと、アラームはアクションを持っていても放送できない。アラーム作成画面からトピックを作ると付くことが多い。トピックを先に手作りした場合は、自分で入れる。</t>
         </is>
       </c>
       <c r="B17" s="25" t="n"/>
       <c r="C17" s="25" t="n"/>
     </row>
     <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>・aws:SourceAccount がワークロードアカウント</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>条件は次の二つを両方入れる。</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
     </row>
     <row r="19" ht="25" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>・aws:SourceArn が、そのリージョンのアラーム ARN（必要ならアラーム名を絞る）</t>
+          <t>・aws:SourceAccount がワークロードアカウント</t>
         </is>
       </c>
       <c r="B19" s="30" t="n"/>
       <c r="C19" s="30" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>プリンシパルは cloudwatch.amazonaws.com にする。Principal: "*" で Publish を開けない。</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>・aws:SourceArn が、そのリージョンのアラーム ARN（必要ならアラーム名を絞る）</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n"/>
+      <c r="C20" s="30" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>暗号化トピックにするなら、KMS キーポリシーが CloudWatch に kms:GenerateDataKey と kms:Decrypt を許す。ここが無いと、Publish が権限で失敗する。</t>
+          <t>プリンシパルは cloudwatch.amazonaws.com にする。Principal: "*" で Publish を開けない。</t>
         </is>
       </c>
       <c r="B21" s="25" t="n"/>
       <c r="C21" s="25" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>暗号化トピックにするなら、KMS キーポリシーが CloudWatch に kms:GenerateDataKey と kms:Decrypt を許す。ここが無いと、Publish が権限で失敗する。</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
@@ -3830,7 +3862,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="59" customHeight="1">
+    <row r="9" ht="76" customHeight="1">
       <c r="A9" s="21" t="inlineStr">
         <is>
           <t>最大メッセージサイズ</t>
@@ -3838,7 +3870,7 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>1バイト〜1 MiB（1,048,576バイト）。コンソールのキュー属性は 1 KiB〜1024 KiB、既定 1024 KiB</t>
+          <t>本文は 1 バイト〜1 MiB（1,048,576 バイト）。キュー属性は 1,024〜1,048,576 バイト、既定 1,048,576（2025年8月以降の新しいキュー）</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -3848,7 +3880,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>アラーム JSON は十分小さい。本文に使える文字は XML、JSON、プレーンテキストと、決められた Unicode 範囲</t>
+          <t>アラーム JSON は数 KB。SNS 経由のときは、キューのこの属性ではなく、トピックの MaximumMessageSize が効く</t>
         </is>
       </c>
     </row>
